--- a/AtchisonRegime/Outputs/USA/USA500_Financials/df_regTrendSummaryUSA500_Financials.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Financials/df_regTrendSummaryUSA500_Financials.xlsx
@@ -846,13 +846,13 @@
         <v>45138</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6129407155433755</v>
+        <v>0.6400680962200578</v>
       </c>
     </row>
   </sheetData>
